--- a/data/raw/additional_species/AFS_FigB_SpeciesRecordingTimePoints.xlsx
+++ b/data/raw/additional_species/AFS_FigB_SpeciesRecordingTimePoints.xlsx
@@ -1,105 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kodom1\Dropbox\ODOM\Pacific\Projects\Side Projects\Acoustic Fine Structure\ML_recs_for_multi_spp_figure\Species For Figure\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EF5AAC-6F7D-4921-89C0-F6C0EE47F477}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="504" yWindow="396" windowWidth="14544" windowHeight="9972" xr2:uid="{D3047389-CF4C-40B5-8E19-B2483180E2F8}"/>
+    <workbookView windowWidth="18615" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Recording</t>
   </si>
   <si>
+    <t>Spectrogram_OneNote_Start(s)</t>
+  </si>
+  <si>
+    <t>Spectrogram_OneNote_End(s)</t>
+  </si>
+  <si>
+    <t>FineStructure_Start(s)</t>
+  </si>
+  <si>
+    <t>FineStructure_End(s)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>ZebraFinch_ML448156111_Calls_Filtered.wav</t>
+  </si>
+  <si>
+    <t>This is a call (not song)</t>
+  </si>
+  <si>
     <t>WhiteCrownedSparrow_ML640519321_OneSong.wav</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>2nd (Buzz) note of the song. The amplitude for this recording is low but the signal to noise ratio is good. You might need to amplify the signal to make it comparable for other spectrograms in this figure.</t>
   </si>
   <si>
     <t>HouseWren_F-HOWR_278013996_2020_T3-1st2020_11452490_11466460_Filtered.wav</t>
   </si>
   <si>
-    <t>Spectrogram_OneNote_Start(s)</t>
-  </si>
-  <si>
-    <t>Spectrogram_OneNote_End(s)</t>
-  </si>
-  <si>
-    <t>FineStructure_Start(s)</t>
-  </si>
-  <si>
-    <t>FineStructure_End(s)</t>
-  </si>
-  <si>
     <t>Female house wren song. 2nd to last note; very buzzy compared to other notes; interesting changes in the direction of the waveform in the subsection I chose.</t>
   </si>
   <si>
-    <t>This is a call (not song)</t>
-  </si>
-  <si>
-    <t>ZebraFinch_ML448156111_Calls_Filtered.wav</t>
-  </si>
-  <si>
     <t>Budgerigar_XC609336_Calls_Filtered.wav</t>
   </si>
   <si>
     <t>Call</t>
   </si>
   <si>
-    <t>Hermit Hummingbird song?</t>
-  </si>
-  <si>
-    <t>I don't have a recording. Marcelo, can you add this on your own, if you want?</t>
+    <t>BlackCappedChickadee_ML54840711_OneCall_Filtered.wav</t>
   </si>
   <si>
     <t>D note (call)</t>
-  </si>
-  <si>
-    <t>BlackCappedChickadee_ML54840711_OneCall_Filtered.wav</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,19 +87,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -127,26 +444,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -195,7 +798,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -228,26 +831,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -280,23 +866,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -438,134 +1007,129 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DB0130-15FC-49BF-A694-5D492E9E657D}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="3" width="25.88671875" customWidth="1"/>
-    <col min="4" max="5" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.8888888888889" customWidth="1"/>
+    <col min="2" max="3" width="25.8888888888889" customWidth="1"/>
+    <col min="4" max="5" width="17.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="B2" s="2">
         <v>1.853464</v>
       </c>
       <c r="C2" s="2">
-        <v>2.0073259999999999</v>
+        <v>2.007326</v>
       </c>
       <c r="D2" s="2">
         <v>1.875008</v>
       </c>
       <c r="E2" s="2">
-        <v>1.8862449999999999</v>
+        <v>1.886245</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1.604707</v>
+      </c>
+      <c r="C3">
+        <v>1.867983</v>
+      </c>
+      <c r="D3">
+        <v>1.762768</v>
+      </c>
+      <c r="E3">
+        <v>1.772933</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1.6047070000000001</v>
-      </c>
-      <c r="C3">
-        <v>1.8679829999999999</v>
-      </c>
-      <c r="D3">
-        <v>1.7627679999999999</v>
-      </c>
-      <c r="E3">
-        <v>1.7729330000000001</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
       <c r="B4">
-        <v>1.2286159999999999</v>
+        <v>1.228616</v>
       </c>
       <c r="C4">
-        <v>1.2837810000000001</v>
+        <v>1.283781</v>
       </c>
       <c r="D4">
-        <v>1.2497290000000001</v>
+        <v>1.249729</v>
       </c>
       <c r="E4">
         <v>1.255458</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
-        <v>4.5620000000000001E-2</v>
+        <v>0.04562</v>
       </c>
       <c r="C5">
-        <v>0.27535399999999999</v>
+        <v>0.275354</v>
       </c>
       <c r="D5">
         <v>0.166074</v>
       </c>
       <c r="E5">
-        <v>0.17457300000000001</v>
+        <v>0.174573</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>1.4282969999999999</v>
+        <v>1.428297</v>
       </c>
       <c r="C6">
-        <v>1.6394390000000001</v>
+        <v>1.639439</v>
       </c>
       <c r="D6">
         <v>1.567912</v>
@@ -574,19 +1138,12 @@
         <v>1.575752</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>